--- a/backend/data/financials_by_company/1458.HK.xlsx
+++ b/backend/data/financials_by_company/1458.HK.xlsx
@@ -652,558 +652,558 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-14104897.086545</v>
+        <v>14704880.618196</v>
       </c>
       <c r="C2" t="n">
-        <v>0.341209</v>
+        <v>0.240728</v>
       </c>
       <c r="D2" t="n">
-        <v>524704000</v>
+        <v>852552000</v>
       </c>
       <c r="E2" t="n">
-        <v>-41338000</v>
+        <v>61085000</v>
       </c>
       <c r="F2" t="n">
-        <v>-41338000</v>
+        <v>61085000</v>
       </c>
       <c r="G2" t="n">
-        <v>98204000</v>
+        <v>342424000</v>
       </c>
       <c r="H2" t="n">
-        <v>321844000</v>
+        <v>402574000</v>
       </c>
       <c r="I2" t="n">
-        <v>1059140000</v>
+        <v>1211570000</v>
       </c>
       <c r="J2" t="n">
-        <v>483366000</v>
+        <v>913637000</v>
       </c>
       <c r="K2" t="n">
-        <v>161522000</v>
+        <v>511063000</v>
       </c>
       <c r="L2" t="n">
-        <v>37591000</v>
+        <v>46807000</v>
       </c>
       <c r="M2" t="n">
-        <v>12455000</v>
+        <v>60073000</v>
       </c>
       <c r="N2" t="n">
-        <v>50046000</v>
+        <v>106880000</v>
       </c>
       <c r="O2" t="n">
-        <v>125437102.913455</v>
+        <v>296043880.618196</v>
       </c>
       <c r="P2" t="n">
-        <v>98204000</v>
+        <v>342424000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2287058000</v>
+        <v>2587517000</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>2195743458</v>
+        <v>2466934831</v>
       </c>
       <c r="T2" t="n">
-        <v>2195460423</v>
+        <v>2312877683</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="W2" t="n">
-        <v>98204000</v>
+        <v>369781000</v>
       </c>
       <c r="X2" t="n">
-        <v>98204000</v>
+        <v>369781000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-27357000</v>
       </c>
       <c r="Z2" t="n">
-        <v>98204000</v>
+        <v>342424000</v>
       </c>
       <c r="AA2" t="n">
-        <v>98204000</v>
+        <v>342424000</v>
       </c>
       <c r="AB2" t="n">
-        <v>98204000</v>
+        <v>342424000</v>
       </c>
       <c r="AC2" t="n">
-        <v>50863000</v>
+        <v>108566000</v>
       </c>
       <c r="AD2" t="n">
-        <v>149067000</v>
+        <v>450990000</v>
       </c>
       <c r="AE2" t="n">
-        <v>991000</v>
+        <v>18684000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-8338000</v>
+        <v>45875000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-5016000</v>
+        <v>-70156000</v>
       </c>
       <c r="AH2" t="n">
-        <v>13354000</v>
+        <v>24281000</v>
       </c>
       <c r="AI2" t="n">
-        <v>37591000</v>
+        <v>46807000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12455000</v>
+        <v>60073000</v>
       </c>
       <c r="AK2" t="n">
-        <v>50046000</v>
+        <v>106880000</v>
       </c>
       <c r="AL2" t="n">
-        <v>163975000</v>
+        <v>282446000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1227918000</v>
+        <v>1375947000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1248629000</v>
+        <v>1394529000</v>
       </c>
       <c r="AO2" t="n">
-        <v>988865000</v>
+        <v>1084919000</v>
       </c>
       <c r="AP2" t="n">
-        <v>259764000</v>
+        <v>309610000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1391893000</v>
+        <v>1658393000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1059140000</v>
+        <v>1211570000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2451033000</v>
+        <v>2869963000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2451033000</v>
+        <v>2869963000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1156750</v>
+        <v>9503500</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>578170000</v>
+        <v>470654000</v>
       </c>
       <c r="E3" t="n">
-        <v>4627000</v>
+        <v>38014000</v>
       </c>
       <c r="F3" t="n">
-        <v>4627000</v>
+        <v>38014000</v>
       </c>
       <c r="G3" t="n">
-        <v>115576000</v>
+        <v>25283000</v>
       </c>
       <c r="H3" t="n">
-        <v>345008000</v>
+        <v>395534000</v>
       </c>
       <c r="I3" t="n">
-        <v>1305467000</v>
+        <v>1053869000</v>
       </c>
       <c r="J3" t="n">
-        <v>582797000</v>
+        <v>508668000</v>
       </c>
       <c r="K3" t="n">
-        <v>237789000</v>
+        <v>113134000</v>
       </c>
       <c r="L3" t="n">
-        <v>48817000</v>
+        <v>9433000</v>
       </c>
       <c r="M3" t="n">
-        <v>23640000</v>
+        <v>58403000</v>
       </c>
       <c r="N3" t="n">
-        <v>72457000</v>
+        <v>67836000</v>
       </c>
       <c r="O3" t="n">
-        <v>112105750</v>
+        <v>-3227500</v>
       </c>
       <c r="P3" t="n">
-        <v>115576000</v>
+        <v>25283000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2592668000</v>
+        <v>2248775000</v>
       </c>
       <c r="R3" t="n">
-        <v>85474000</v>
+        <v>56737000</v>
       </c>
       <c r="S3" t="n">
-        <v>2318041930</v>
+        <v>2439839090</v>
       </c>
       <c r="T3" t="n">
-        <v>2316332731</v>
+        <v>2311223096</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05</v>
+        <v>0.026119</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05</v>
+        <v>0.027572</v>
       </c>
       <c r="W3" t="n">
-        <v>115576000</v>
+        <v>63725000</v>
       </c>
       <c r="X3" t="n">
-        <v>115576000</v>
+        <v>63725000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-38442000</v>
       </c>
       <c r="Z3" t="n">
-        <v>115576000</v>
+        <v>25283000</v>
       </c>
       <c r="AA3" t="n">
-        <v>115576000</v>
+        <v>25283000</v>
       </c>
       <c r="AB3" t="n">
-        <v>115576000</v>
+        <v>25283000</v>
       </c>
       <c r="AC3" t="n">
-        <v>98573000</v>
+        <v>29448000</v>
       </c>
       <c r="AD3" t="n">
-        <v>214149000</v>
+        <v>54731000</v>
       </c>
       <c r="AE3" t="n">
-        <v>6493000</v>
+        <v>13822000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8018000</v>
+        <v>45732000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-21802000</v>
+        <v>-66044000</v>
       </c>
       <c r="AH3" t="n">
-        <v>13784000</v>
+        <v>20312000</v>
       </c>
       <c r="AI3" t="n">
-        <v>48817000</v>
+        <v>9433000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23640000</v>
+        <v>58403000</v>
       </c>
       <c r="AK3" t="n">
-        <v>72457000</v>
+        <v>67836000</v>
       </c>
       <c r="AL3" t="n">
-        <v>150960000</v>
+        <v>94578000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1287201000</v>
+        <v>1194906000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1299931000</v>
+        <v>1240925000</v>
       </c>
       <c r="AO3" t="n">
-        <v>982970000</v>
+        <v>930509000</v>
       </c>
       <c r="AP3" t="n">
-        <v>316961000</v>
+        <v>310416000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1438161000</v>
+        <v>1289484000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1305467000</v>
+        <v>1053869000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2743628000</v>
+        <v>2343353000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2743628000</v>
+        <v>2343353000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>9503500</v>
+        <v>1156750</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>470654000</v>
+        <v>578170000</v>
       </c>
       <c r="E4" t="n">
-        <v>38014000</v>
+        <v>4627000</v>
       </c>
       <c r="F4" t="n">
-        <v>38014000</v>
+        <v>4627000</v>
       </c>
       <c r="G4" t="n">
-        <v>25283000</v>
+        <v>115576000</v>
       </c>
       <c r="H4" t="n">
-        <v>395534000</v>
+        <v>345008000</v>
       </c>
       <c r="I4" t="n">
-        <v>1053869000</v>
+        <v>1305467000</v>
       </c>
       <c r="J4" t="n">
-        <v>508668000</v>
+        <v>582797000</v>
       </c>
       <c r="K4" t="n">
-        <v>113134000</v>
+        <v>237789000</v>
       </c>
       <c r="L4" t="n">
-        <v>9433000</v>
+        <v>48817000</v>
       </c>
       <c r="M4" t="n">
-        <v>58403000</v>
+        <v>23640000</v>
       </c>
       <c r="N4" t="n">
-        <v>67836000</v>
+        <v>72457000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3227500</v>
+        <v>112105750</v>
       </c>
       <c r="P4" t="n">
-        <v>25283000</v>
+        <v>115576000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2248775000</v>
+        <v>2592668000</v>
       </c>
       <c r="R4" t="n">
-        <v>56737000</v>
+        <v>85474000</v>
       </c>
       <c r="S4" t="n">
-        <v>2439839090</v>
+        <v>2318041930</v>
       </c>
       <c r="T4" t="n">
-        <v>2311223096</v>
+        <v>2316332731</v>
       </c>
       <c r="U4" t="n">
-        <v>0.026119</v>
+        <v>0.05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.027572</v>
+        <v>0.05</v>
       </c>
       <c r="W4" t="n">
-        <v>63725000</v>
+        <v>115576000</v>
       </c>
       <c r="X4" t="n">
-        <v>63725000</v>
+        <v>115576000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-38442000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>25283000</v>
+        <v>115576000</v>
       </c>
       <c r="AA4" t="n">
-        <v>25283000</v>
+        <v>115576000</v>
       </c>
       <c r="AB4" t="n">
-        <v>25283000</v>
+        <v>115576000</v>
       </c>
       <c r="AC4" t="n">
-        <v>29448000</v>
+        <v>98573000</v>
       </c>
       <c r="AD4" t="n">
-        <v>54731000</v>
+        <v>214149000</v>
       </c>
       <c r="AE4" t="n">
-        <v>13822000</v>
+        <v>6493000</v>
       </c>
       <c r="AF4" t="n">
-        <v>45732000</v>
+        <v>8018000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-66044000</v>
+        <v>-21802000</v>
       </c>
       <c r="AH4" t="n">
-        <v>20312000</v>
+        <v>13784000</v>
       </c>
       <c r="AI4" t="n">
-        <v>9433000</v>
+        <v>48817000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>58403000</v>
+        <v>23640000</v>
       </c>
       <c r="AK4" t="n">
-        <v>67836000</v>
+        <v>72457000</v>
       </c>
       <c r="AL4" t="n">
-        <v>94578000</v>
+        <v>150960000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1194906000</v>
+        <v>1287201000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1240925000</v>
+        <v>1299931000</v>
       </c>
       <c r="AO4" t="n">
-        <v>930509000</v>
+        <v>982970000</v>
       </c>
       <c r="AP4" t="n">
-        <v>310416000</v>
+        <v>316961000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1289484000</v>
+        <v>1438161000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1053869000</v>
+        <v>1305467000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2343353000</v>
+        <v>2743628000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2343353000</v>
+        <v>2743628000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>14704880.618196</v>
+        <v>-14104897.086545</v>
       </c>
       <c r="C5" t="n">
-        <v>0.240728</v>
+        <v>0.341209</v>
       </c>
       <c r="D5" t="n">
-        <v>852552000</v>
+        <v>524704000</v>
       </c>
       <c r="E5" t="n">
-        <v>61085000</v>
+        <v>-41338000</v>
       </c>
       <c r="F5" t="n">
-        <v>61085000</v>
+        <v>-41338000</v>
       </c>
       <c r="G5" t="n">
-        <v>342424000</v>
+        <v>98204000</v>
       </c>
       <c r="H5" t="n">
-        <v>402574000</v>
+        <v>321844000</v>
       </c>
       <c r="I5" t="n">
-        <v>1211570000</v>
+        <v>1059140000</v>
       </c>
       <c r="J5" t="n">
-        <v>913637000</v>
+        <v>483366000</v>
       </c>
       <c r="K5" t="n">
-        <v>511063000</v>
+        <v>161522000</v>
       </c>
       <c r="L5" t="n">
-        <v>46807000</v>
+        <v>37591000</v>
       </c>
       <c r="M5" t="n">
-        <v>60073000</v>
+        <v>12455000</v>
       </c>
       <c r="N5" t="n">
-        <v>106880000</v>
+        <v>50046000</v>
       </c>
       <c r="O5" t="n">
-        <v>296043880.618196</v>
+        <v>125437102.913455</v>
       </c>
       <c r="P5" t="n">
-        <v>342424000</v>
+        <v>98204000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2587517000</v>
+        <v>2287058000</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>2466934831</v>
+        <v>2195743458</v>
       </c>
       <c r="T5" t="n">
-        <v>2312877683</v>
+        <v>2195460423</v>
       </c>
       <c r="U5" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="V5" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="W5" t="n">
-        <v>369781000</v>
+        <v>98204000</v>
       </c>
       <c r="X5" t="n">
-        <v>369781000</v>
+        <v>98204000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-27357000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>342424000</v>
+        <v>98204000</v>
       </c>
       <c r="AA5" t="n">
-        <v>342424000</v>
+        <v>98204000</v>
       </c>
       <c r="AB5" t="n">
-        <v>342424000</v>
+        <v>98204000</v>
       </c>
       <c r="AC5" t="n">
-        <v>108566000</v>
+        <v>50863000</v>
       </c>
       <c r="AD5" t="n">
-        <v>450990000</v>
+        <v>149067000</v>
       </c>
       <c r="AE5" t="n">
-        <v>18684000</v>
+        <v>991000</v>
       </c>
       <c r="AF5" t="n">
-        <v>45875000</v>
+        <v>-8338000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-70156000</v>
+        <v>-5016000</v>
       </c>
       <c r="AH5" t="n">
-        <v>24281000</v>
+        <v>13354000</v>
       </c>
       <c r="AI5" t="n">
-        <v>46807000</v>
+        <v>37591000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>60073000</v>
+        <v>12455000</v>
       </c>
       <c r="AK5" t="n">
-        <v>106880000</v>
+        <v>50046000</v>
       </c>
       <c r="AL5" t="n">
-        <v>282446000</v>
+        <v>163975000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1375947000</v>
+        <v>1227918000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1394529000</v>
+        <v>1248629000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1084919000</v>
+        <v>988865000</v>
       </c>
       <c r="AP5" t="n">
-        <v>309610000</v>
+        <v>259764000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1658393000</v>
+        <v>1391893000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1211570000</v>
+        <v>1059140000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2869963000</v>
+        <v>2451033000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2869963000</v>
+        <v>2451033000</v>
       </c>
     </row>
   </sheetData>
@@ -1604,283 +1604,287 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>107099074</v>
+        <v>74713043</v>
       </c>
       <c r="C2" t="n">
-        <v>2100268426</v>
+        <v>2308427457</v>
       </c>
       <c r="D2" t="n">
-        <v>2207367500</v>
+        <v>2383140500</v>
       </c>
       <c r="E2" t="n">
-        <v>373084000</v>
+        <v>1659304000</v>
       </c>
       <c r="F2" t="n">
-        <v>3613296000</v>
+        <v>4182526000</v>
       </c>
       <c r="G2" t="n">
-        <v>3776503000</v>
+        <v>5493661000</v>
       </c>
       <c r="H2" t="n">
-        <v>1126949000</v>
+        <v>2921109000</v>
       </c>
       <c r="I2" t="n">
-        <v>3613296000</v>
+        <v>4182526000</v>
       </c>
       <c r="J2" t="n">
-        <v>223084000</v>
+        <v>375951000</v>
       </c>
       <c r="K2" t="n">
-        <v>3626503000</v>
+        <v>4210308000</v>
       </c>
       <c r="L2" t="n">
-        <v>3626503000</v>
+        <v>5443661000</v>
       </c>
       <c r="M2" t="n">
-        <v>3626503000</v>
+        <v>4210308000</v>
       </c>
       <c r="N2" t="n">
-        <v>3626503000</v>
+        <v>4210308000</v>
       </c>
       <c r="O2" t="n">
-        <v>10764000</v>
+        <v>26998000</v>
       </c>
       <c r="P2" t="n">
-        <v>458592000</v>
+        <v>341445000</v>
       </c>
       <c r="Q2" t="n">
-        <v>3231434000</v>
+        <v>3025875000</v>
       </c>
       <c r="R2" t="n">
-        <v>673834000</v>
+        <v>1434892000</v>
       </c>
       <c r="S2" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="T2" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="U2" t="n">
-        <v>961289000</v>
+        <v>2427727000</v>
       </c>
       <c r="V2" t="n">
-        <v>195536000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>1560815000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>36105000</v>
+      </c>
       <c r="X2" t="n">
-        <v>50388000</v>
+        <v>87403000</v>
       </c>
       <c r="Y2" t="n">
-        <v>63377000</v>
+        <v>55409000</v>
       </c>
       <c r="Z2" t="n">
-        <v>81771000</v>
+        <v>1418003000</v>
       </c>
       <c r="AA2" t="n">
-        <v>81771000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>184650000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1233353000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>765753000</v>
+        <v>866912000</v>
       </c>
       <c r="AD2" t="n">
-        <v>54054000</v>
+        <v>82079000</v>
       </c>
       <c r="AE2" t="n">
-        <v>291313000</v>
+        <v>241301000</v>
       </c>
       <c r="AF2" t="n">
-        <v>141313000</v>
+        <v>191301000</v>
       </c>
       <c r="AG2" t="n">
-        <v>150000000</v>
+        <v>50000000</v>
       </c>
       <c r="AH2" t="n">
-        <v>287755000</v>
+        <v>400361000</v>
       </c>
       <c r="AI2" t="n">
-        <v>190234000</v>
+        <v>260660000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40461000</v>
+        <v>61768000</v>
       </c>
       <c r="AK2" t="n">
-        <v>57060000</v>
+        <v>77933000</v>
       </c>
       <c r="AL2" t="n">
-        <v>4587792000</v>
+        <v>6638035000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2695090000</v>
+        <v>2850014000</v>
       </c>
       <c r="AN2" t="n">
-        <v>258401000</v>
+        <v>94575000</v>
       </c>
       <c r="AO2" t="n">
-        <v>125524000</v>
+        <v>84145000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2500000</v>
-      </c>
+        <v>120000000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>627848000</v>
+        <v>569271000</v>
       </c>
       <c r="AT2" t="n">
-        <v>627848000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10247000</v>
-      </c>
+        <v>569271000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>13207000</v>
+        <v>27782000</v>
       </c>
       <c r="AW2" t="n">
-        <v>13207000</v>
+        <v>27782000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1650845000</v>
+        <v>1954241000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-679164000</v>
+        <v>-485625000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2330009000</v>
+        <v>2439866000</v>
       </c>
       <c r="BA2" t="n">
-        <v>93044000</v>
+        <v>277706000</v>
       </c>
       <c r="BB2" t="n">
-        <v>68643000</v>
+        <v>88485000</v>
       </c>
       <c r="BC2" t="n">
-        <v>575851000</v>
+        <v>492988000</v>
       </c>
       <c r="BD2" t="n">
-        <v>1477015000</v>
+        <v>1456663000</v>
       </c>
       <c r="BE2" t="n">
-        <v>115456000</v>
+        <v>124024000</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>1892702000</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
+        <v>3788021000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1092000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>58189000</v>
+        <v>62077000</v>
       </c>
       <c r="BL2" t="n">
-        <v>226853000</v>
+        <v>321937000</v>
       </c>
       <c r="BM2" t="n">
-        <v>33076000</v>
+        <v>46433000</v>
       </c>
       <c r="BN2" t="n">
-        <v>5894000</v>
+        <v>815000</v>
       </c>
       <c r="BO2" t="n">
-        <v>187883000</v>
+        <v>274689000</v>
       </c>
       <c r="BP2" t="n">
-        <v>14530000</v>
+        <v>48749000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>57282000</v>
+        <v>62034000</v>
       </c>
       <c r="BR2" t="n">
-        <v>67925000</v>
+        <v>73571000</v>
       </c>
       <c r="BS2" t="n">
-        <v>-16882000</v>
+        <v>-1335000</v>
       </c>
       <c r="BT2" t="n">
-        <v>84807000</v>
+        <v>74906000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1467923000</v>
+        <v>3219653000</v>
       </c>
       <c r="BV2" t="n">
-        <v>213766000</v>
+        <v>1117308000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1254157000</v>
+        <v>2102345000</v>
       </c>
       <c r="BX2" t="n">
-        <v>770900000</v>
+        <v>1829760000</v>
       </c>
       <c r="BY2" t="n">
-        <v>483257000</v>
+        <v>272585000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>90814419</v>
+        <v>70930057</v>
       </c>
       <c r="C3" t="n">
-        <v>2292326081</v>
+        <v>2312210443</v>
       </c>
       <c r="D3" t="n">
         <v>2383140500</v>
       </c>
       <c r="E3" t="n">
-        <v>287912000</v>
+        <v>953068000</v>
       </c>
       <c r="F3" t="n">
-        <v>3922144000</v>
+        <v>4068516000</v>
       </c>
       <c r="G3" t="n">
-        <v>3935410000</v>
+        <v>4687988000</v>
       </c>
       <c r="H3" t="n">
-        <v>1446641000</v>
+        <v>1928943000</v>
       </c>
       <c r="I3" t="n">
-        <v>3922144000</v>
+        <v>4068516000</v>
       </c>
       <c r="J3" t="n">
-        <v>287912000</v>
+        <v>353389000</v>
       </c>
       <c r="K3" t="n">
-        <v>3935410000</v>
+        <v>4088309000</v>
       </c>
       <c r="L3" t="n">
-        <v>3935410000</v>
+        <v>4527988000</v>
       </c>
       <c r="M3" t="n">
-        <v>3935410000</v>
+        <v>4088309000</v>
       </c>
       <c r="N3" t="n">
-        <v>3935410000</v>
+        <v>4088309000</v>
       </c>
       <c r="O3" t="n">
-        <v>39690000</v>
+        <v>41217000</v>
       </c>
       <c r="P3" t="n">
-        <v>350181000</v>
+        <v>324459000</v>
       </c>
       <c r="Q3" t="n">
-        <v>3147155000</v>
+        <v>3036988000</v>
       </c>
       <c r="R3" t="n">
-        <v>952212000</v>
+        <v>1203698000</v>
       </c>
       <c r="S3" t="n">
         <v>16000</v>
@@ -1889,65 +1893,67 @@
         <v>16000</v>
       </c>
       <c r="U3" t="n">
-        <v>957849000</v>
+        <v>1643410000</v>
       </c>
       <c r="V3" t="n">
-        <v>273665000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>728841000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>32850000</v>
+      </c>
       <c r="X3" t="n">
-        <v>66864000</v>
+        <v>82324000</v>
       </c>
       <c r="Y3" t="n">
-        <v>92165000</v>
+        <v>56134000</v>
       </c>
       <c r="Z3" t="n">
-        <v>114636000</v>
+        <v>590383000</v>
       </c>
       <c r="AA3" t="n">
-        <v>114636000</v>
+        <v>150704000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>439679000</v>
       </c>
       <c r="AC3" t="n">
-        <v>684184000</v>
+        <v>914569000</v>
       </c>
       <c r="AD3" t="n">
-        <v>50784000</v>
+        <v>51579000</v>
       </c>
       <c r="AE3" t="n">
-        <v>173276000</v>
+        <v>362685000</v>
       </c>
       <c r="AF3" t="n">
-        <v>173276000</v>
+        <v>202685000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>160000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>347193000</v>
+        <v>367763000</v>
       </c>
       <c r="AI3" t="n">
-        <v>200820000</v>
+        <v>219621000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>49971000</v>
+        <v>40698000</v>
       </c>
       <c r="AK3" t="n">
-        <v>96402000</v>
+        <v>107444000</v>
       </c>
       <c r="AL3" t="n">
-        <v>4893259000</v>
+        <v>5731719000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2762434000</v>
+        <v>2888207000</v>
       </c>
       <c r="AN3" t="n">
-        <v>95175000</v>
+        <v>94195000</v>
       </c>
       <c r="AO3" t="n">
-        <v>103714000</v>
+        <v>105106000</v>
       </c>
       <c r="AP3" t="n">
         <v>122500000</v>
@@ -1959,155 +1965,153 @@
         <v>120000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>631501000</v>
+        <v>633246000</v>
       </c>
       <c r="AT3" t="n">
-        <v>631501000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
+        <v>633246000</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>13266000</v>
+        <v>19793000</v>
       </c>
       <c r="AW3" t="n">
-        <v>13266000</v>
+        <v>19793000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1789760000</v>
+        <v>1907209000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-622727000</v>
+        <v>-601150000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2412487000</v>
+        <v>2508359000</v>
       </c>
       <c r="BA3" t="n">
-        <v>157811000</v>
+        <v>339651000</v>
       </c>
       <c r="BB3" t="n">
-        <v>77749000</v>
+        <v>87157000</v>
       </c>
       <c r="BC3" t="n">
-        <v>501822000</v>
+        <v>502094000</v>
       </c>
       <c r="BD3" t="n">
-        <v>1556793000</v>
+        <v>1458289000</v>
       </c>
       <c r="BE3" t="n">
-        <v>118312000</v>
+        <v>121168000</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>2130825000</v>
+        <v>2843512000</v>
       </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>4000000</v>
+        <v>100000000</v>
       </c>
       <c r="BK3" t="n">
-        <v>56113000</v>
+        <v>63909000</v>
       </c>
       <c r="BL3" t="n">
-        <v>315320000</v>
+        <v>280726000</v>
       </c>
       <c r="BM3" t="n">
-        <v>41717000</v>
+        <v>33748000</v>
       </c>
       <c r="BN3" t="n">
-        <v>5975000</v>
+        <v>2114000</v>
       </c>
       <c r="BO3" t="n">
-        <v>267628000</v>
+        <v>244864000</v>
       </c>
       <c r="BP3" t="n">
-        <v>41633000</v>
+        <v>34543000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>63273000</v>
+        <v>37614000</v>
       </c>
       <c r="BR3" t="n">
-        <v>61260000</v>
+        <v>56037000</v>
       </c>
       <c r="BS3" t="n">
-        <v>-16999000</v>
+        <v>-7260000</v>
       </c>
       <c r="BT3" t="n">
-        <v>78259000</v>
+        <v>63297000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1589226000</v>
+        <v>2270683000</v>
       </c>
       <c r="BV3" t="n">
-        <v>514749000</v>
+        <v>1024735000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1074477000</v>
+        <v>1245948000</v>
       </c>
       <c r="BX3" t="n">
-        <v>796907000</v>
+        <v>1034630000</v>
       </c>
       <c r="BY3" t="n">
-        <v>277570000</v>
+        <v>211318000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>70930057</v>
+        <v>90814419</v>
       </c>
       <c r="C4" t="n">
-        <v>2312210443</v>
+        <v>2292326081</v>
       </c>
       <c r="D4" t="n">
         <v>2383140500</v>
       </c>
       <c r="E4" t="n">
-        <v>953068000</v>
+        <v>287912000</v>
       </c>
       <c r="F4" t="n">
-        <v>4068516000</v>
+        <v>3922144000</v>
       </c>
       <c r="G4" t="n">
-        <v>4687988000</v>
+        <v>3935410000</v>
       </c>
       <c r="H4" t="n">
-        <v>1928943000</v>
+        <v>1446641000</v>
       </c>
       <c r="I4" t="n">
-        <v>4068516000</v>
+        <v>3922144000</v>
       </c>
       <c r="J4" t="n">
-        <v>353389000</v>
+        <v>287912000</v>
       </c>
       <c r="K4" t="n">
-        <v>4088309000</v>
+        <v>3935410000</v>
       </c>
       <c r="L4" t="n">
-        <v>4527988000</v>
+        <v>3935410000</v>
       </c>
       <c r="M4" t="n">
-        <v>4088309000</v>
+        <v>3935410000</v>
       </c>
       <c r="N4" t="n">
-        <v>4088309000</v>
+        <v>3935410000</v>
       </c>
       <c r="O4" t="n">
-        <v>41217000</v>
+        <v>39690000</v>
       </c>
       <c r="P4" t="n">
-        <v>324459000</v>
+        <v>350181000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3036988000</v>
+        <v>3147155000</v>
       </c>
       <c r="R4" t="n">
-        <v>1203698000</v>
+        <v>952212000</v>
       </c>
       <c r="S4" t="n">
         <v>16000</v>
@@ -2116,67 +2120,65 @@
         <v>16000</v>
       </c>
       <c r="U4" t="n">
-        <v>1643410000</v>
+        <v>957849000</v>
       </c>
       <c r="V4" t="n">
-        <v>728841000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>32850000</v>
-      </c>
+        <v>273665000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>82324000</v>
+        <v>66864000</v>
       </c>
       <c r="Y4" t="n">
-        <v>56134000</v>
+        <v>92165000</v>
       </c>
       <c r="Z4" t="n">
-        <v>590383000</v>
+        <v>114636000</v>
       </c>
       <c r="AA4" t="n">
-        <v>150704000</v>
+        <v>114636000</v>
       </c>
       <c r="AB4" t="n">
-        <v>439679000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>914569000</v>
+        <v>684184000</v>
       </c>
       <c r="AD4" t="n">
-        <v>51579000</v>
+        <v>50784000</v>
       </c>
       <c r="AE4" t="n">
-        <v>362685000</v>
+        <v>173276000</v>
       </c>
       <c r="AF4" t="n">
-        <v>202685000</v>
+        <v>173276000</v>
       </c>
       <c r="AG4" t="n">
-        <v>160000000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>367763000</v>
+        <v>347193000</v>
       </c>
       <c r="AI4" t="n">
-        <v>219621000</v>
+        <v>200820000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40698000</v>
+        <v>49971000</v>
       </c>
       <c r="AK4" t="n">
-        <v>107444000</v>
+        <v>96402000</v>
       </c>
       <c r="AL4" t="n">
-        <v>5731719000</v>
+        <v>4893259000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2888207000</v>
+        <v>2762434000</v>
       </c>
       <c r="AN4" t="n">
-        <v>94195000</v>
+        <v>95175000</v>
       </c>
       <c r="AO4" t="n">
-        <v>105106000</v>
+        <v>103714000</v>
       </c>
       <c r="AP4" t="n">
         <v>122500000</v>
@@ -2188,326 +2190,324 @@
         <v>120000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>633246000</v>
+        <v>631501000</v>
       </c>
       <c r="AT4" t="n">
-        <v>633246000</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
+        <v>631501000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
       <c r="AV4" t="n">
-        <v>19793000</v>
+        <v>13266000</v>
       </c>
       <c r="AW4" t="n">
-        <v>19793000</v>
+        <v>13266000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1907209000</v>
+        <v>1789760000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-601150000</v>
+        <v>-622727000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2508359000</v>
+        <v>2412487000</v>
       </c>
       <c r="BA4" t="n">
-        <v>339651000</v>
+        <v>157811000</v>
       </c>
       <c r="BB4" t="n">
-        <v>87157000</v>
+        <v>77749000</v>
       </c>
       <c r="BC4" t="n">
-        <v>502094000</v>
+        <v>501822000</v>
       </c>
       <c r="BD4" t="n">
-        <v>1458289000</v>
+        <v>1556793000</v>
       </c>
       <c r="BE4" t="n">
-        <v>121168000</v>
+        <v>118312000</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>2843512000</v>
+        <v>2130825000</v>
       </c>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>100000000</v>
+        <v>4000000</v>
       </c>
       <c r="BK4" t="n">
-        <v>63909000</v>
+        <v>56113000</v>
       </c>
       <c r="BL4" t="n">
-        <v>280726000</v>
+        <v>315320000</v>
       </c>
       <c r="BM4" t="n">
-        <v>33748000</v>
+        <v>41717000</v>
       </c>
       <c r="BN4" t="n">
-        <v>2114000</v>
+        <v>5975000</v>
       </c>
       <c r="BO4" t="n">
-        <v>244864000</v>
+        <v>267628000</v>
       </c>
       <c r="BP4" t="n">
-        <v>34543000</v>
+        <v>41633000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>37614000</v>
+        <v>63273000</v>
       </c>
       <c r="BR4" t="n">
-        <v>56037000</v>
+        <v>61260000</v>
       </c>
       <c r="BS4" t="n">
-        <v>-7260000</v>
+        <v>-16999000</v>
       </c>
       <c r="BT4" t="n">
-        <v>63297000</v>
+        <v>78259000</v>
       </c>
       <c r="BU4" t="n">
-        <v>2270683000</v>
+        <v>1589226000</v>
       </c>
       <c r="BV4" t="n">
-        <v>1024735000</v>
+        <v>514749000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1245948000</v>
+        <v>1074477000</v>
       </c>
       <c r="BX4" t="n">
-        <v>1034630000</v>
+        <v>796907000</v>
       </c>
       <c r="BY4" t="n">
-        <v>211318000</v>
+        <v>277570000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>74713043</v>
+        <v>107099074</v>
       </c>
       <c r="C5" t="n">
-        <v>2308427457</v>
+        <v>2100268426</v>
       </c>
       <c r="D5" t="n">
-        <v>2383140500</v>
+        <v>2207367500</v>
       </c>
       <c r="E5" t="n">
-        <v>1659304000</v>
+        <v>373084000</v>
       </c>
       <c r="F5" t="n">
-        <v>4182526000</v>
+        <v>3613296000</v>
       </c>
       <c r="G5" t="n">
-        <v>5493661000</v>
+        <v>3776503000</v>
       </c>
       <c r="H5" t="n">
-        <v>2921109000</v>
+        <v>1126949000</v>
       </c>
       <c r="I5" t="n">
-        <v>4182526000</v>
+        <v>3613296000</v>
       </c>
       <c r="J5" t="n">
-        <v>375951000</v>
+        <v>223084000</v>
       </c>
       <c r="K5" t="n">
-        <v>4210308000</v>
+        <v>3626503000</v>
       </c>
       <c r="L5" t="n">
-        <v>5443661000</v>
+        <v>3626503000</v>
       </c>
       <c r="M5" t="n">
-        <v>4210308000</v>
+        <v>3626503000</v>
       </c>
       <c r="N5" t="n">
-        <v>4210308000</v>
+        <v>3626503000</v>
       </c>
       <c r="O5" t="n">
-        <v>26998000</v>
+        <v>10764000</v>
       </c>
       <c r="P5" t="n">
-        <v>341445000</v>
+        <v>458592000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3025875000</v>
+        <v>3231434000</v>
       </c>
       <c r="R5" t="n">
-        <v>1434892000</v>
+        <v>673834000</v>
       </c>
       <c r="S5" t="n">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="T5" t="n">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="U5" t="n">
-        <v>2427727000</v>
+        <v>961289000</v>
       </c>
       <c r="V5" t="n">
-        <v>1560815000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>36105000</v>
-      </c>
+        <v>195536000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>87403000</v>
+        <v>50388000</v>
       </c>
       <c r="Y5" t="n">
-        <v>55409000</v>
+        <v>63377000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1418003000</v>
+        <v>81771000</v>
       </c>
       <c r="AA5" t="n">
-        <v>184650000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1233353000</v>
-      </c>
+        <v>81771000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>866912000</v>
+        <v>765753000</v>
       </c>
       <c r="AD5" t="n">
-        <v>82079000</v>
+        <v>54054000</v>
       </c>
       <c r="AE5" t="n">
-        <v>241301000</v>
+        <v>291313000</v>
       </c>
       <c r="AF5" t="n">
-        <v>191301000</v>
+        <v>141313000</v>
       </c>
       <c r="AG5" t="n">
-        <v>50000000</v>
+        <v>150000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>400361000</v>
+        <v>287755000</v>
       </c>
       <c r="AI5" t="n">
-        <v>260660000</v>
+        <v>190234000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>61768000</v>
+        <v>40461000</v>
       </c>
       <c r="AK5" t="n">
-        <v>77933000</v>
+        <v>57060000</v>
       </c>
       <c r="AL5" t="n">
-        <v>6638035000</v>
+        <v>4587792000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2850014000</v>
+        <v>2695090000</v>
       </c>
       <c r="AN5" t="n">
-        <v>94575000</v>
+        <v>258401000</v>
       </c>
       <c r="AO5" t="n">
-        <v>84145000</v>
+        <v>125524000</v>
       </c>
       <c r="AP5" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>2500000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2500000</v>
+      </c>
       <c r="AR5" t="n">
-        <v>120000000</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>569271000</v>
+        <v>627848000</v>
       </c>
       <c r="AT5" t="n">
-        <v>569271000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>627848000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10247000</v>
+      </c>
       <c r="AV5" t="n">
-        <v>27782000</v>
+        <v>13207000</v>
       </c>
       <c r="AW5" t="n">
-        <v>27782000</v>
+        <v>13207000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1954241000</v>
+        <v>1650845000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-485625000</v>
+        <v>-679164000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2439866000</v>
+        <v>2330009000</v>
       </c>
       <c r="BA5" t="n">
-        <v>277706000</v>
+        <v>93044000</v>
       </c>
       <c r="BB5" t="n">
-        <v>88485000</v>
+        <v>68643000</v>
       </c>
       <c r="BC5" t="n">
-        <v>492988000</v>
+        <v>575851000</v>
       </c>
       <c r="BD5" t="n">
-        <v>1456663000</v>
+        <v>1477015000</v>
       </c>
       <c r="BE5" t="n">
-        <v>124024000</v>
+        <v>115456000</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>3788021000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1092000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
+        <v>1892702000</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>62077000</v>
+        <v>58189000</v>
       </c>
       <c r="BL5" t="n">
-        <v>321937000</v>
+        <v>226853000</v>
       </c>
       <c r="BM5" t="n">
-        <v>46433000</v>
+        <v>33076000</v>
       </c>
       <c r="BN5" t="n">
-        <v>815000</v>
+        <v>5894000</v>
       </c>
       <c r="BO5" t="n">
-        <v>274689000</v>
+        <v>187883000</v>
       </c>
       <c r="BP5" t="n">
-        <v>48749000</v>
+        <v>14530000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>62034000</v>
+        <v>57282000</v>
       </c>
       <c r="BR5" t="n">
-        <v>73571000</v>
+        <v>67925000</v>
       </c>
       <c r="BS5" t="n">
-        <v>-1335000</v>
+        <v>-16882000</v>
       </c>
       <c r="BT5" t="n">
-        <v>74906000</v>
+        <v>84807000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3219653000</v>
+        <v>1467923000</v>
       </c>
       <c r="BV5" t="n">
-        <v>1117308000</v>
+        <v>213766000</v>
       </c>
       <c r="BW5" t="n">
-        <v>2102345000</v>
+        <v>1254157000</v>
       </c>
       <c r="BX5" t="n">
-        <v>1829760000</v>
+        <v>770900000</v>
       </c>
       <c r="BY5" t="n">
-        <v>272585000</v>
+        <v>483257000</v>
       </c>
     </row>
   </sheetData>
@@ -2818,73 +2818,73 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>352977000</v>
+        <v>328667000</v>
       </c>
       <c r="C2" t="n">
-        <v>-316806000</v>
+        <v>-83286000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-450765000</v>
       </c>
       <c r="E2" t="n">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>13659000</v>
       </c>
       <c r="G2" t="n">
-        <v>-63410000</v>
+        <v>-211167000</v>
       </c>
       <c r="H2" t="n">
-        <v>805456000</v>
+        <v>271493000</v>
       </c>
       <c r="I2" t="n">
-        <v>384477000</v>
+        <v>271401000</v>
       </c>
       <c r="J2" t="n">
-        <v>371000</v>
+        <v>-11996000</v>
       </c>
       <c r="K2" t="n">
-        <v>420608000</v>
+        <v>12088000</v>
       </c>
       <c r="L2" t="n">
-        <v>-477870000</v>
+        <v>-470117000</v>
       </c>
       <c r="M2" t="n">
-        <v>4000000</v>
+        <v>384066000</v>
       </c>
       <c r="N2" t="n">
-        <v>-2223000</v>
+        <v>-13765000</v>
       </c>
       <c r="O2" t="n">
-        <v>-100588000</v>
+        <v>-154668000</v>
       </c>
       <c r="P2" t="n">
-        <v>-100588000</v>
+        <v>-154668000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-316806000</v>
+        <v>-69627000</v>
       </c>
       <c r="R2" t="n">
-        <v>-316806000</v>
+        <v>-83286000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>13659000</v>
       </c>
       <c r="T2" t="n">
-        <v>150000000</v>
+        <v>-350765000</v>
       </c>
       <c r="U2" t="n">
-        <v>150000000</v>
+        <v>-350765000</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-450765000</v>
       </c>
       <c r="W2" t="n">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -2892,522 +2892,526 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>100000000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>482091000</v>
+        <v>-57629000</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>68792000</v>
+        <v>103418000</v>
       </c>
       <c r="AD2" t="n">
-        <v>465267000</v>
+        <v>191907000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1781048000</v>
+        <v>4412177000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1315781000</v>
+        <v>-4220270000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1213000</v>
+        <v>-209068000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1213000</v>
+        <v>58447000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-267515000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-5207000</v>
+        <v>-5961000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-5207000</v>
+        <v>-5961000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-47974000</v>
+        <v>-137925000</v>
       </c>
       <c r="AM2" t="n">
-        <v>10229000</v>
+        <v>67281000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-58203000</v>
+        <v>-205206000</v>
       </c>
       <c r="AO2" t="n">
-        <v>416387000</v>
+        <v>539834000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-110019000</v>
+        <v>-88894000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-10232000</v>
+        <v>-17321000</v>
       </c>
       <c r="AR2" t="n">
-        <v>49852000</v>
+        <v>-76835000</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-1024000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-37446000</v>
+        <v>-9604000</v>
       </c>
       <c r="AU2" t="n">
-        <v>7853000</v>
+        <v>9195000</v>
       </c>
       <c r="AV2" t="n">
-        <v>88467000</v>
+        <v>-66746000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-9022000</v>
+        <v>-8656000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-44984000</v>
+        <v>-55759000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-4113000</v>
+        <v>26797000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>321844000</v>
+        <v>402574000</v>
       </c>
       <c r="BA2" t="n">
-        <v>5630000</v>
+        <v>9319000</v>
       </c>
       <c r="BB2" t="n">
-        <v>316214000</v>
+        <v>393255000</v>
       </c>
       <c r="BC2" t="n">
-        <v>37015000</v>
+        <v>-15210000</v>
       </c>
       <c r="BD2" t="n">
-        <v>8655000</v>
+        <v>-14396000</v>
       </c>
       <c r="BE2" t="n">
-        <v>94000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>-38816000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-31340000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>149067000</v>
+        <v>450990000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>268802000</v>
+        <v>307217000</v>
       </c>
       <c r="C3" t="n">
-        <v>-51709000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-684960000</v>
+        <v>-936534000</v>
       </c>
       <c r="E3" t="n">
-        <v>60000000</v>
+        <v>160000000</v>
       </c>
       <c r="F3" t="n">
-        <v>11878000</v>
+        <v>10614000</v>
       </c>
       <c r="G3" t="n">
-        <v>-92378000</v>
+        <v>-160422000</v>
       </c>
       <c r="H3" t="n">
-        <v>384477000</v>
+        <v>487541000</v>
       </c>
       <c r="I3" t="n">
-        <v>487541000</v>
+        <v>271493000</v>
       </c>
       <c r="J3" t="n">
-        <v>19092000</v>
+        <v>22341000</v>
       </c>
       <c r="K3" t="n">
-        <v>-122156000</v>
+        <v>193707000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1046487000</v>
+        <v>-1318294000</v>
       </c>
       <c r="M3" t="n">
-        <v>96000000</v>
+        <v>-100000000</v>
       </c>
       <c r="N3" t="n">
-        <v>-4846000</v>
+        <v>-16125000</v>
       </c>
       <c r="O3" t="n">
-        <v>-257955000</v>
+        <v>-236286000</v>
       </c>
       <c r="P3" t="n">
-        <v>-257955000</v>
+        <v>-236286000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-39831000</v>
+        <v>10614000</v>
       </c>
       <c r="R3" t="n">
-        <v>-51709000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>11878000</v>
+        <v>10614000</v>
       </c>
       <c r="T3" t="n">
-        <v>-624960000</v>
+        <v>-776534000</v>
       </c>
       <c r="U3" t="n">
-        <v>-160000000</v>
+        <v>110000000</v>
       </c>
       <c r="V3" t="n">
-        <v>-220000000</v>
+        <v>-50000000</v>
       </c>
       <c r="W3" t="n">
-        <v>60000000</v>
+        <v>160000000</v>
       </c>
       <c r="X3" t="n">
-        <v>-464960000</v>
+        <v>-886534000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-464960000</v>
+        <v>-886534000</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>563151000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>1044362000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>459000</v>
+      </c>
       <c r="AC3" t="n">
-        <v>64658000</v>
+        <v>71941000</v>
       </c>
       <c r="AD3" t="n">
-        <v>577953000</v>
+        <v>1175656000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1954140000</v>
+        <v>5567409000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1376187000</v>
+        <v>-4391753000</v>
       </c>
       <c r="AG3" t="n">
-        <v>4036000</v>
+        <v>-54901000</v>
       </c>
       <c r="AH3" t="n">
-        <v>5116000</v>
+        <v>22500000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1080000</v>
+        <v>-77401000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2445000</v>
+        <v>-2436000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2445000</v>
+        <v>-2436000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-81051000</v>
+        <v>-140357000</v>
       </c>
       <c r="AM3" t="n">
-        <v>8882000</v>
+        <v>17629000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-89933000</v>
+        <v>-157986000</v>
       </c>
       <c r="AO3" t="n">
-        <v>361180000</v>
+        <v>467639000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-52952000</v>
+        <v>-63014000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-12539000</v>
+        <v>-16997000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-107647000</v>
+        <v>42185000</v>
       </c>
       <c r="AS3" t="n">
-        <v>700000</v>
+        <v>392000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-26540000</v>
+        <v>-28860000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-32251000</v>
+        <v>17833000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-34594000</v>
+        <v>41211000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-14962000</v>
+        <v>11609000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-67726000</v>
+        <v>-60053000</v>
       </c>
       <c r="AY3" t="n">
-        <v>24401000</v>
+        <v>32768000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>345008000</v>
+        <v>395534000</v>
       </c>
       <c r="BA3" t="n">
-        <v>10474000</v>
+        <v>12551000</v>
       </c>
       <c r="BB3" t="n">
-        <v>334534000</v>
+        <v>382983000</v>
       </c>
       <c r="BC3" t="n">
-        <v>3391000</v>
+        <v>7718000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-2166000</v>
+        <v>109074000</v>
       </c>
       <c r="BE3" t="n">
-        <v>3383000</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>-1673000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
       <c r="BG3" t="n">
-        <v>214149000</v>
+        <v>54731000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>307217000</v>
+        <v>268802000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-51709000</v>
       </c>
       <c r="D4" t="n">
-        <v>-936534000</v>
+        <v>-684960000</v>
       </c>
       <c r="E4" t="n">
-        <v>160000000</v>
+        <v>60000000</v>
       </c>
       <c r="F4" t="n">
-        <v>10614000</v>
+        <v>11878000</v>
       </c>
       <c r="G4" t="n">
-        <v>-160422000</v>
+        <v>-92378000</v>
       </c>
       <c r="H4" t="n">
+        <v>384477000</v>
+      </c>
+      <c r="I4" t="n">
         <v>487541000</v>
       </c>
-      <c r="I4" t="n">
-        <v>271493000</v>
-      </c>
       <c r="J4" t="n">
-        <v>22341000</v>
+        <v>19092000</v>
       </c>
       <c r="K4" t="n">
-        <v>193707000</v>
+        <v>-122156000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1318294000</v>
+        <v>-1046487000</v>
       </c>
       <c r="M4" t="n">
-        <v>-100000000</v>
+        <v>96000000</v>
       </c>
       <c r="N4" t="n">
-        <v>-16125000</v>
+        <v>-4846000</v>
       </c>
       <c r="O4" t="n">
-        <v>-236286000</v>
+        <v>-257955000</v>
       </c>
       <c r="P4" t="n">
-        <v>-236286000</v>
+        <v>-257955000</v>
       </c>
       <c r="Q4" t="n">
-        <v>10614000</v>
+        <v>-39831000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-51709000</v>
       </c>
       <c r="S4" t="n">
-        <v>10614000</v>
+        <v>11878000</v>
       </c>
       <c r="T4" t="n">
-        <v>-776534000</v>
+        <v>-624960000</v>
       </c>
       <c r="U4" t="n">
-        <v>110000000</v>
+        <v>-160000000</v>
       </c>
       <c r="V4" t="n">
-        <v>-50000000</v>
+        <v>-220000000</v>
       </c>
       <c r="W4" t="n">
-        <v>160000000</v>
+        <v>60000000</v>
       </c>
       <c r="X4" t="n">
-        <v>-886534000</v>
+        <v>-464960000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-886534000</v>
+        <v>-464960000</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>1044362000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>459000</v>
-      </c>
+        <v>563151000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>71941000</v>
+        <v>64658000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1175656000</v>
+        <v>577953000</v>
       </c>
       <c r="AE4" t="n">
-        <v>5567409000</v>
+        <v>1954140000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4391753000</v>
+        <v>-1376187000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-54901000</v>
+        <v>4036000</v>
       </c>
       <c r="AH4" t="n">
-        <v>22500000</v>
+        <v>5116000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-77401000</v>
+        <v>-1080000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2436000</v>
+        <v>-2445000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-2436000</v>
+        <v>-2445000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-140357000</v>
+        <v>-81051000</v>
       </c>
       <c r="AM4" t="n">
-        <v>17629000</v>
+        <v>8882000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-157986000</v>
+        <v>-89933000</v>
       </c>
       <c r="AO4" t="n">
-        <v>467639000</v>
+        <v>361180000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-63014000</v>
+        <v>-52952000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-16997000</v>
+        <v>-12539000</v>
       </c>
       <c r="AR4" t="n">
-        <v>42185000</v>
+        <v>-107647000</v>
       </c>
       <c r="AS4" t="n">
-        <v>392000</v>
+        <v>700000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-28860000</v>
+        <v>-26540000</v>
       </c>
       <c r="AU4" t="n">
-        <v>17833000</v>
+        <v>-32251000</v>
       </c>
       <c r="AV4" t="n">
-        <v>41211000</v>
+        <v>-34594000</v>
       </c>
       <c r="AW4" t="n">
-        <v>11609000</v>
+        <v>-14962000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-60053000</v>
+        <v>-67726000</v>
       </c>
       <c r="AY4" t="n">
-        <v>32768000</v>
+        <v>24401000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>395534000</v>
+        <v>345008000</v>
       </c>
       <c r="BA4" t="n">
-        <v>12551000</v>
+        <v>10474000</v>
       </c>
       <c r="BB4" t="n">
-        <v>382983000</v>
+        <v>334534000</v>
       </c>
       <c r="BC4" t="n">
-        <v>7718000</v>
+        <v>3391000</v>
       </c>
       <c r="BD4" t="n">
-        <v>109074000</v>
+        <v>-2166000</v>
       </c>
       <c r="BE4" t="n">
-        <v>-1673000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
+        <v>3383000</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>54731000</v>
+        <v>214149000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>328667000</v>
+        <v>352977000</v>
       </c>
       <c r="C5" t="n">
-        <v>-83286000</v>
+        <v>-316806000</v>
       </c>
       <c r="D5" t="n">
-        <v>-450765000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="F5" t="n">
-        <v>13659000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-211167000</v>
+        <v>-63410000</v>
       </c>
       <c r="H5" t="n">
-        <v>271493000</v>
+        <v>805456000</v>
       </c>
       <c r="I5" t="n">
-        <v>271401000</v>
+        <v>384477000</v>
       </c>
       <c r="J5" t="n">
-        <v>-11996000</v>
+        <v>371000</v>
       </c>
       <c r="K5" t="n">
-        <v>12088000</v>
+        <v>420608000</v>
       </c>
       <c r="L5" t="n">
-        <v>-470117000</v>
+        <v>-477870000</v>
       </c>
       <c r="M5" t="n">
-        <v>384066000</v>
+        <v>4000000</v>
       </c>
       <c r="N5" t="n">
-        <v>-13765000</v>
+        <v>-2223000</v>
       </c>
       <c r="O5" t="n">
-        <v>-154668000</v>
+        <v>-100588000</v>
       </c>
       <c r="P5" t="n">
-        <v>-154668000</v>
+        <v>-100588000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-69627000</v>
+        <v>-316806000</v>
       </c>
       <c r="R5" t="n">
-        <v>-83286000</v>
+        <v>-316806000</v>
       </c>
       <c r="S5" t="n">
-        <v>13659000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-350765000</v>
+        <v>150000000</v>
       </c>
       <c r="U5" t="n">
-        <v>-350765000</v>
+        <v>150000000</v>
       </c>
       <c r="V5" t="n">
-        <v>-450765000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -3415,105 +3419,101 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>100000000</v>
-      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-57629000</v>
+        <v>482091000</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>103418000</v>
+        <v>68792000</v>
       </c>
       <c r="AD5" t="n">
-        <v>191907000</v>
+        <v>465267000</v>
       </c>
       <c r="AE5" t="n">
-        <v>4412177000</v>
+        <v>1781048000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4220270000</v>
+        <v>-1315781000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-209068000</v>
+        <v>1213000</v>
       </c>
       <c r="AH5" t="n">
-        <v>58447000</v>
+        <v>1213000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-267515000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-5961000</v>
+        <v>-5207000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-5961000</v>
+        <v>-5207000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-137925000</v>
+        <v>-47974000</v>
       </c>
       <c r="AM5" t="n">
-        <v>67281000</v>
+        <v>10229000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-205206000</v>
+        <v>-58203000</v>
       </c>
       <c r="AO5" t="n">
-        <v>539834000</v>
+        <v>416387000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-88894000</v>
+        <v>-110019000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-17321000</v>
+        <v>-10232000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-76835000</v>
+        <v>49852000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1024000</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-9604000</v>
+        <v>-37446000</v>
       </c>
       <c r="AU5" t="n">
-        <v>9195000</v>
+        <v>7853000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-66746000</v>
+        <v>88467000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-8656000</v>
+        <v>-9022000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-55759000</v>
+        <v>-44984000</v>
       </c>
       <c r="AY5" t="n">
-        <v>26797000</v>
+        <v>-4113000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>402574000</v>
+        <v>321844000</v>
       </c>
       <c r="BA5" t="n">
-        <v>9319000</v>
+        <v>5630000</v>
       </c>
       <c r="BB5" t="n">
-        <v>393255000</v>
+        <v>316214000</v>
       </c>
       <c r="BC5" t="n">
-        <v>-15210000</v>
+        <v>37015000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-14396000</v>
+        <v>8655000</v>
       </c>
       <c r="BE5" t="n">
-        <v>-38816000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-31340000</v>
-      </c>
+        <v>94000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>450990000</v>
+        <v>149067000</v>
       </c>
     </row>
   </sheetData>
@@ -4113,197 +4113,197 @@
       </c>
       <c r="DM1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EZ1" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Fuyu  Zhou', 'age': 50, 'title': 'CEO &amp; Executive Chairman', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 3719755, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hanbin  Lyu', 'age': 49, 'title': 'Chief Supply Chain Officer &amp; Executive Director', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 3848342, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yali  Wang', 'age': 48, 'title': 'GM of Central Warzone &amp; Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 1138748, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xiang  Wang', 'age': 42, 'title': 'Financial Director', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Pak Yu  Tam A.C.I.S., A.C.S.', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Fuyu  Zhou', 'age': 50, 'title': 'CEO &amp; Executive Chairman', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 3716791, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hanbin  Lyu', 'age': 49, 'title': 'Chief Supply Chain Officer &amp; Executive Director', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 3845275, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yali  Wang', 'age': 48, 'title': 'GM of Central Warzone &amp; Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 1137840, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xiang  Wang', 'age': 42, 'title': 'Financial Director', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Pak Yu  Tam A.C.I.S., A.C.S.', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4411,28 +4411,28 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
         <v>0.09</v>
@@ -4447,34 +4447,34 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.109</v>
+        <v>0.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>15.777777</v>
+        <v>14.111111</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11.865886</v>
+        <v>10.618165</v>
       </c>
       <c r="AK2" t="n">
-        <v>685500</v>
+        <v>1156000</v>
       </c>
       <c r="AL2" t="n">
-        <v>685500</v>
+        <v>1156000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2830169</v>
+        <v>2672644</v>
       </c>
       <c r="AN2" t="n">
-        <v>2050600</v>
+        <v>1297194</v>
       </c>
       <c r="AO2" t="n">
-        <v>2050600</v>
+        <v>1297194</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4483,13 +4483,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>2806810112</v>
+        <v>2503797760</v>
       </c>
       <c r="AU2" t="n">
-        <v>2866108823</v>
+        <v>2566172407</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AW2" t="n">
         <v>2.85</v>
@@ -4498,22 +4498,22 @@
         <v>11.86</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.1066777</v>
+        <v>0.98720497</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.4916</v>
+        <v>1.4762</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.74745</v>
+        <v>1.6744</v>
       </c>
       <c r="BC2" t="n">
         <v>0.08</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.05517241</v>
+        <v>0.06153846</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -4524,31 +4524,31 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>2415719168</v>
+        <v>2107428480</v>
       </c>
       <c r="BH2" t="n">
         <v>0.06178</v>
       </c>
       <c r="BI2" t="n">
-        <v>679513789</v>
+        <v>674786665</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1976626775</v>
+        <v>1971494275</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.64294</v>
+        <v>0.65278</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.02725</v>
+        <v>0.02648</v>
       </c>
       <c r="BM2" t="n">
-        <v>1976626775</v>
+        <v>1971494275</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.991033</v>
+        <v>1.9897736</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.7131976</v>
+        <v>0.6382635</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -4569,19 +4569,19 @@
         <v>0.09</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.11967079</v>
+        <v>0.11960635</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.952</v>
+        <v>0.831</v>
       </c>
       <c r="BX2" t="n">
-        <v>7.913</v>
+        <v>6.903</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.44015443</v>
+        <v>-0.4605809</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CA2" t="n">
         <v>0.05</v>
@@ -4595,19 +4595,19 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="CE2" t="n">
-        <v>2.423373</v>
+        <v>2.4198165</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.127981</v>
+        <v>2.124858</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.3013587</v>
+        <v>2.2979813</v>
       </c>
       <c r="CH2" t="n">
-        <v>2.3527105</v>
+        <v>2.3492577</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -4717,144 +4717,144 @@
           <t>PRE</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Zhou Hei Ya International Holdings Company Limited</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>finmb_406473162</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>ZHOU HEI YA</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.029999971</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>1.22 - 1.27</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>2672644</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.049999952</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.040983565</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>1.22 - 2.85</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>-1.5799999</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.55438596</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-46.05809</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1755773940</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1756123200</v>
+      </c>
+      <c r="EJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0.11960635</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.09333</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>13.607628</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.2062</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.13968298</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.4044</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.24151935</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-2.3076901</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="EX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EY2" t="n">
         <v>1478827800000</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.03000009</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>1.42 - 1.45</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>2830169</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.15999997</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.1269841</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>1.26 - 2.85</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.5017544</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-44.01544</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1755773940</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>ZHOU HEI YA</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Zhou Hei Ya International Holdings Company Limited</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>1756123200</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>1</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.11967079</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.09333</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>15.2148285</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.07160008</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.0480022</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-0.32745004</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.18738736</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-2.0689716</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="ER2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>finmb_406473162</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EW2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EY2" t="b">
-        <v>0</v>
       </c>
       <c r="EZ2" t="inlineStr"/>
     </row>
